--- a/KAZAN_BOT_AB_BACA_DUZENLI.xlsx
+++ b/KAZAN_BOT_AB_BACA_DUZENLI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9769EBF-6A98-4490-BACA-BC86F9FE8C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE23D1D-074F-4465-9FEF-B771B4E24339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="288" yWindow="864" windowWidth="22752" windowHeight="12096" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1404" yWindow="0" windowWidth="22752" windowHeight="12096" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KAZANLAR" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
   <si>
     <t>Güç (kW)</t>
   </si>
@@ -37,9 +37,6 @@
   </si>
   <si>
     <t>Ürün Adı</t>
-  </si>
-  <si>
-    <t>ListeFiyatı (€)</t>
   </si>
   <si>
     <t>DK05</t>
@@ -196,7 +193,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;₺&quot;_-;\-* #,##0.00\ &quot;₺&quot;_-;_-* &quot;-&quot;??\ &quot;₺&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,6 +229,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="162"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="5">
@@ -273,7 +275,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -300,6 +302,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Köprü 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -471,14 +474,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="3" width="14.77734375" customWidth="1"/>
     <col min="4" max="4" width="10.88671875" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -491,11 +494,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E1" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>50</v>
       </c>
@@ -503,16 +506,16 @@
         <v>8006724000</v>
       </c>
       <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
       </c>
       <c r="E2">
         <v>1600</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>65</v>
       </c>
@@ -520,16 +523,16 @@
         <v>8006720000</v>
       </c>
       <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
         <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
       </c>
       <c r="E3">
         <v>1700</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>100</v>
       </c>
@@ -537,16 +540,16 @@
         <v>8006721000</v>
       </c>
       <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
         <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
       </c>
       <c r="E4">
         <v>2050</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>125</v>
       </c>
@@ -554,16 +557,16 @@
         <v>8006722000</v>
       </c>
       <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
         <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
       </c>
       <c r="E5">
         <v>2300</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>150</v>
       </c>
@@ -571,10 +574,10 @@
         <v>8006723000</v>
       </c>
       <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
         <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
       </c>
       <c r="E6">
         <v>2950</v>
@@ -588,7 +591,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="6.77734375" customWidth="1"/>
     <col min="2" max="2" width="8.77734375" customWidth="1"/>
@@ -596,9 +599,9 @@
     <col min="4" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="28.8">
       <c r="A1" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>1</v>
@@ -607,98 +610,98 @@
         <v>3</v>
       </c>
       <c r="D1" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C2" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="D2">
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="D3">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="D4">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="D5">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="D6">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="D7">
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
         <v>42</v>
-      </c>
-      <c r="B8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
       </c>
       <c r="D8">
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
         <v>44</v>
-      </c>
-      <c r="B9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
       </c>
       <c r="D9">
         <v>190</v>
@@ -712,14 +715,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="47.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="28.8">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -728,37 +731,37 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D2">
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="D3">
         <v>340</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" s="4">
         <v>150</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>400</v>
@@ -772,27 +775,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>37</v>
       </c>
       <c r="B2">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>38</v>
@@ -806,26 +809,26 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.6640625" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="6.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="28.8">
       <c r="A1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>41</v>
-      </c>
       <c r="D1" s="7"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -836,7 +839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>17</v>
       </c>
@@ -847,7 +850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>33</v>
       </c>
@@ -858,7 +861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>49</v>
       </c>
@@ -877,84 +880,84 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.33203125" customWidth="1"/>
     <col min="2" max="2" width="5.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="B3" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="B4" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="28.8">
+      <c r="A5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>52</v>
       </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>53</v>
-      </c>
       <c r="B7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/KAZAN_BOT_AB_BACA_DUZENLI.xlsx
+++ b/KAZAN_BOT_AB_BACA_DUZENLI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE23D1D-074F-4465-9FEF-B771B4E24339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6081D9-FF48-49E2-9246-2B65C27F17DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1404" yWindow="0" windowWidth="22752" windowHeight="12096" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KAZANLAR" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
   <si>
     <t>Güç (kW)</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>HER_TEKLIF</t>
+  </si>
+  <si>
+    <t>LISTE FIYATI (€)</t>
   </si>
 </sst>
 </file>
@@ -495,7 +498,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:5">
